--- a/lib/assets/templates/template_siswa.xlsx
+++ b/lib/assets/templates/template_siswa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project_TA\si_lapor\lib\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED66808-C4FA-4453-B10C-52A4046358B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8219178-CC2E-4A34-8B03-1C363C0E8018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{87D1E045-727B-472A-B289-5C95EB54DCF1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87D1E045-727B-472A-B289-5C95EB54DCF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>nama_lengkap</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>jumlah_juz</t>
   </si>
 </sst>
 </file>
@@ -73,7 +76,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -108,7 +111,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,13 +446,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D76348C-505B-43C1-AD38-8460AC6E373A}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +474,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -493,6 +499,9 @@
       </c>
       <c r="G2">
         <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
